--- a/Horarios/Colectivos/322-Lujan/LaboralMarcosPaz.xlsx
+++ b/Horarios/Colectivos/322-Lujan/LaboralMarcosPaz.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>135_104013-1</t>
+          <t>135_104002-1</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>135_104014-1</t>
+          <t>135_104003-1</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>135_104015-1</t>
+          <t>135_104004-1</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -752,7 +752,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>
